--- a/extracted/reports/tramos_filtrado_estricto/tramo_175+260_175+285.xlsx
+++ b/extracted/reports/tramos_filtrado_estricto/tramo_175+260_175+285.xlsx
@@ -463,7 +463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F40"/>
+  <dimension ref="A1:F48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -485,14 +485,14 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Filtro estricto: INICIO (KM) y FIN (KM) contenidos en el tramo | Total registros: 29</t>
+          <t>Filtro: FIN completo contenido en tramo; FIN en blanco si INICIO cae en tramo | Total registros: 37</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Año 2022 (1 registros)</t>
+          <t>Año 2022 (3 registros)</t>
         </is>
       </c>
       <c r="B4" s="2" t="n"/>
@@ -564,331 +564,315 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>Limpieza de Superfície de Concreto y Dispos. Drenaje T2</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>2022-07-13</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>175+265</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="n"/>
+      <c r="F7" s="5" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>Sellado de juntas de cunetas T2</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>2022-07-14</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>175+265</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="n"/>
+      <c r="F8" s="5" t="n">
+        <v>13.5</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>Año 2023 (1 registros)</t>
         </is>
       </c>
-      <c r="B7" s="2" t="n"/>
-      <c r="C7" s="2" t="n"/>
-      <c r="D7" s="2" t="n"/>
-      <c r="E7" s="2" t="n"/>
-      <c r="F7" s="2" t="n"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="3" t="inlineStr">
+      <c r="B9" s="2" t="n"/>
+      <c r="C9" s="2" t="n"/>
+      <c r="D9" s="2" t="n"/>
+      <c r="E9" s="2" t="n"/>
+      <c r="F9" s="2" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
         <is>
           <t>Descripción</t>
         </is>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B10" s="3" t="inlineStr">
         <is>
           <t>Unidad</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="C10" s="3" t="inlineStr">
         <is>
           <t>Fecha</t>
         </is>
       </c>
-      <c r="D8" s="3" t="inlineStr">
+      <c r="D10" s="3" t="inlineStr">
         <is>
           <t>INICIO (KM)</t>
         </is>
       </c>
-      <c r="E8" s="3" t="inlineStr">
+      <c r="E10" s="3" t="inlineStr">
         <is>
           <t>FIN (KM)</t>
         </is>
       </c>
-      <c r="F8" s="3" t="inlineStr">
+      <c r="F10" s="3" t="inlineStr">
         <is>
           <t>METRADO</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="4" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
         <is>
           <t>Limpieza de Guardavías T2</t>
         </is>
       </c>
-      <c r="B9" s="5" t="inlineStr">
+      <c r="B11" s="5" t="inlineStr">
         <is>
           <t>ml</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C11" s="5" t="inlineStr">
         <is>
           <t>2023-10-10</t>
         </is>
       </c>
-      <c r="D9" s="5" t="inlineStr">
-        <is>
-          <t>175+260</t>
-        </is>
-      </c>
-      <c r="E9" s="5" t="inlineStr">
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>175+260</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
         <is>
           <t>175+282</t>
         </is>
       </c>
-      <c r="F9" s="5" t="n">
+      <c r="F11" s="5" t="n">
         <v>22</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>Año 2024 (1 registros)</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="n"/>
-      <c r="C10" s="2" t="n"/>
-      <c r="D10" s="2" t="n"/>
-      <c r="E10" s="2" t="n"/>
-      <c r="F10" s="2" t="n"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="3" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>Año 2024 (3 registros)</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n"/>
+      <c r="C12" s="2" t="n"/>
+      <c r="D12" s="2" t="n"/>
+      <c r="E12" s="2" t="n"/>
+      <c r="F12" s="2" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
         <is>
           <t>Descripción</t>
         </is>
       </c>
-      <c r="B11" s="3" t="inlineStr">
+      <c r="B13" s="3" t="inlineStr">
         <is>
           <t>Unidad</t>
         </is>
       </c>
-      <c r="C11" s="3" t="inlineStr">
+      <c r="C13" s="3" t="inlineStr">
         <is>
           <t>Fecha</t>
         </is>
       </c>
-      <c r="D11" s="3" t="inlineStr">
+      <c r="D13" s="3" t="inlineStr">
         <is>
           <t>INICIO (KM)</t>
         </is>
       </c>
-      <c r="E11" s="3" t="inlineStr">
+      <c r="E13" s="3" t="inlineStr">
         <is>
           <t>FIN (KM)</t>
         </is>
       </c>
-      <c r="F11" s="3" t="inlineStr">
+      <c r="F13" s="3" t="inlineStr">
         <is>
           <t>METRADO</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="4" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
         <is>
           <t>Limpieza de Deslizamientos Menores &lt; 15 m3 T2</t>
         </is>
       </c>
-      <c r="B12" s="5" t="inlineStr">
+      <c r="B14" s="5" t="inlineStr">
         <is>
           <t>m3</t>
         </is>
       </c>
-      <c r="C12" s="5" t="inlineStr">
+      <c r="C14" s="5" t="inlineStr">
         <is>
           <t>2024-01-15</t>
         </is>
       </c>
-      <c r="D12" s="5" t="inlineStr">
+      <c r="D14" s="5" t="inlineStr">
         <is>
           <t>175+265</t>
         </is>
       </c>
-      <c r="E12" s="5" t="inlineStr">
+      <c r="E14" s="5" t="inlineStr">
         <is>
           <t>175+280</t>
         </is>
       </c>
-      <c r="F12" s="5" t="n">
+      <c r="F14" s="5" t="n">
         <v>15</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>Año 2025 (26 registros)</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="n"/>
-      <c r="C13" s="2" t="n"/>
-      <c r="D13" s="2" t="n"/>
-      <c r="E13" s="2" t="n"/>
-      <c r="F13" s="2" t="n"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="3" t="inlineStr">
-        <is>
-          <t>Descripción</t>
-        </is>
-      </c>
-      <c r="B14" s="3" t="inlineStr">
-        <is>
-          <t>Unidad</t>
-        </is>
-      </c>
-      <c r="C14" s="3" t="inlineStr">
-        <is>
-          <t>Fecha</t>
-        </is>
-      </c>
-      <c r="D14" s="3" t="inlineStr">
-        <is>
-          <t>INICIO (KM)</t>
-        </is>
-      </c>
-      <c r="E14" s="3" t="inlineStr">
-        <is>
-          <t>FIN (KM)</t>
-        </is>
-      </c>
-      <c r="F14" s="3" t="inlineStr">
-        <is>
-          <t>METRADO</t>
-        </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>Limpieza de Deslizamientos Menores &lt; 15 m3 T2</t>
+          <t>Limpieza Manual de Cuneta de Vía T2</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>m3</t>
+          <t>ml</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>2025-02-26</t>
+          <t>2024-01-19</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>175+260</t>
-        </is>
-      </c>
-      <c r="E15" s="5" t="inlineStr">
-        <is>
-          <t>175+270</t>
-        </is>
-      </c>
+          <t>175+265</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="n"/>
       <c r="F15" s="5" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>Limpieza Manual de Cuneta de Vía T2</t>
+          <t>Pintura Chevron Guarda Vías T2</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>ml</t>
+          <t>m2</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>2025-03-25</t>
+          <t>2024-02-09</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>175+260</t>
-        </is>
-      </c>
-      <c r="E16" s="5" t="inlineStr">
-        <is>
-          <t>175+270</t>
-        </is>
-      </c>
+          <t>175+285</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="n"/>
       <c r="F16" s="5" t="n">
-        <v>100</v>
+        <v>6</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="4" t="inlineStr">
-        <is>
-          <t>Limpieza Manual de Cuneta de Vía T2</t>
-        </is>
-      </c>
-      <c r="B17" s="5" t="inlineStr">
-        <is>
-          <t>ml</t>
-        </is>
-      </c>
-      <c r="C17" s="5" t="inlineStr">
-        <is>
-          <t>2025-03-26</t>
-        </is>
-      </c>
-      <c r="D17" s="5" t="inlineStr">
-        <is>
-          <t>175+260</t>
-        </is>
-      </c>
-      <c r="E17" s="5" t="inlineStr">
-        <is>
-          <t>175+270</t>
-        </is>
-      </c>
-      <c r="F17" s="5" t="n">
-        <v>100</v>
-      </c>
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>Año 2025 (30 registros)</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n"/>
+      <c r="C17" s="2" t="n"/>
+      <c r="D17" s="2" t="n"/>
+      <c r="E17" s="2" t="n"/>
+      <c r="F17" s="2" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="4" t="inlineStr">
-        <is>
-          <t>Remocion de Derrumbes T2</t>
-        </is>
-      </c>
-      <c r="B18" s="5" t="inlineStr">
-        <is>
-          <t>m3</t>
-        </is>
-      </c>
-      <c r="C18" s="5" t="inlineStr">
-        <is>
-          <t>2025-03-27</t>
-        </is>
-      </c>
-      <c r="D18" s="5" t="inlineStr">
-        <is>
-          <t>175+260</t>
-        </is>
-      </c>
-      <c r="E18" s="5" t="inlineStr">
-        <is>
-          <t>175+270</t>
-        </is>
-      </c>
-      <c r="F18" s="5" t="n">
-        <v>105</v>
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>Descripción</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>Unidad</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>Fecha</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>INICIO (KM)</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>FIN (KM)</t>
+        </is>
+      </c>
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t>METRADO</t>
+        </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>Limpieza de carril/pista y bermas T2</t>
+          <t>Limpieza de Deslizamientos Menores &lt; 15 m3 T2</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>m2</t>
+          <t>m3</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>2025-03-27</t>
+          <t>2025-02-26</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
@@ -902,7 +886,7 @@
         </is>
       </c>
       <c r="F19" s="5" t="n">
-        <v>100</v>
+        <v>15</v>
       </c>
     </row>
     <row r="20">
@@ -918,7 +902,7 @@
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>2025-04-04</t>
+          <t>2025-03-25</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
@@ -928,11 +912,11 @@
       </c>
       <c r="E20" s="5" t="inlineStr">
         <is>
-          <t>175+285</t>
+          <t>175+270</t>
         </is>
       </c>
       <c r="F20" s="5" t="n">
-        <v>120</v>
+        <v>100</v>
       </c>
     </row>
     <row r="21">
@@ -948,7 +932,7 @@
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>2025-04-06</t>
+          <t>2025-03-26</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
@@ -958,7 +942,7 @@
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t>175+285</t>
+          <t>175+270</t>
         </is>
       </c>
       <c r="F21" s="5" t="n">
@@ -968,17 +952,17 @@
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>Limpieza Manual de Cuneta de Vía T2</t>
+          <t>Remocion de Derrumbes T2</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>ml</t>
+          <t>m3</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>2025-04-06</t>
+          <t>2025-03-27</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
@@ -988,27 +972,27 @@
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t>175+285</t>
+          <t>175+270</t>
         </is>
       </c>
       <c r="F22" s="5" t="n">
-        <v>100</v>
+        <v>105</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>Remocion de Derrumbes T2</t>
+          <t>Limpieza de carril/pista y bermas T2</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>m3</t>
+          <t>m2</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>2025-04-07</t>
+          <t>2025-03-27</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
@@ -1018,27 +1002,27 @@
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t>175+285</t>
+          <t>175+270</t>
         </is>
       </c>
       <c r="F23" s="5" t="n">
-        <v>60</v>
+        <v>100</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>Remocion de Derrumbes T2</t>
+          <t>Limpieza Manual de Cuneta de Vía T2</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>m3</t>
+          <t>ml</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>2025-04-07</t>
+          <t>2025-04-04</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
@@ -1052,23 +1036,23 @@
         </is>
       </c>
       <c r="F24" s="5" t="n">
-        <v>15</v>
+        <v>120</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>Remocion de Derrumbes T2</t>
+          <t>Limpieza Manual de Cuneta de Vía T2</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>m3</t>
+          <t>ml</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>2025-04-08</t>
+          <t>2025-04-06</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
@@ -1082,23 +1066,23 @@
         </is>
       </c>
       <c r="F25" s="5" t="n">
-        <v>135</v>
+        <v>100</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t>Remocion de Derrumbes T2</t>
+          <t>Limpieza Manual de Cuneta de Vía T2</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>m3</t>
+          <t>ml</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>2025-04-09</t>
+          <t>2025-04-06</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
@@ -1112,7 +1096,7 @@
         </is>
       </c>
       <c r="F26" s="5" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
     </row>
     <row r="27">
@@ -1128,7 +1112,7 @@
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>2025-04-09</t>
+          <t>2025-04-07</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
@@ -1142,7 +1126,7 @@
         </is>
       </c>
       <c r="F27" s="5" t="n">
-        <v>45</v>
+        <v>60</v>
       </c>
     </row>
     <row r="28">
@@ -1158,7 +1142,7 @@
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>2025-04-11</t>
+          <t>2025-04-07</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
@@ -1172,7 +1156,7 @@
         </is>
       </c>
       <c r="F28" s="5" t="n">
-        <v>45</v>
+        <v>15</v>
       </c>
     </row>
     <row r="29">
@@ -1188,7 +1172,7 @@
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>2025-04-14</t>
+          <t>2025-04-08</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
@@ -1218,7 +1202,7 @@
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>2025-04-16</t>
+          <t>2025-04-09</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
@@ -1232,23 +1216,23 @@
         </is>
       </c>
       <c r="F30" s="5" t="n">
-        <v>330</v>
+        <v>90</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>Limpieza de carril/pista y bermas T2</t>
+          <t>Remocion de Derrumbes T2</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>m2</t>
+          <t>m3</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>2025-04-18</t>
+          <t>2025-04-09</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
@@ -1262,7 +1246,7 @@
         </is>
       </c>
       <c r="F31" s="5" t="n">
-        <v>25</v>
+        <v>45</v>
       </c>
     </row>
     <row r="32">
@@ -1278,7 +1262,7 @@
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>2025-04-21</t>
+          <t>2025-04-11</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
@@ -1292,7 +1276,7 @@
         </is>
       </c>
       <c r="F32" s="5" t="n">
-        <v>135</v>
+        <v>45</v>
       </c>
     </row>
     <row r="33">
@@ -1308,7 +1292,7 @@
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>2025-04-22</t>
+          <t>2025-04-14</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
@@ -1322,7 +1306,7 @@
         </is>
       </c>
       <c r="F33" s="5" t="n">
-        <v>75</v>
+        <v>135</v>
       </c>
     </row>
     <row r="34">
@@ -1338,7 +1322,7 @@
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>2025-04-26</t>
+          <t>2025-04-16</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
@@ -1352,23 +1336,23 @@
         </is>
       </c>
       <c r="F34" s="5" t="n">
-        <v>135</v>
+        <v>330</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
         <is>
-          <t>Remocion de Derrumbes T2</t>
+          <t>Limpieza de carril/pista y bermas T2</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>m3</t>
+          <t>m2</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>2025-04-27</t>
+          <t>2025-04-18</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
@@ -1382,7 +1366,7 @@
         </is>
       </c>
       <c r="F35" s="5" t="n">
-        <v>195</v>
+        <v>25</v>
       </c>
     </row>
     <row r="36">
@@ -1398,7 +1382,7 @@
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>2025-05-11</t>
+          <t>2025-04-21</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
@@ -1412,13 +1396,13 @@
         </is>
       </c>
       <c r="F36" s="5" t="n">
-        <v>30</v>
+        <v>135</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
         <is>
-          <t>Limpieza de Deslizamientos Menores &lt; 15 m3 T2</t>
+          <t>Remocion de Derrumbes T2</t>
         </is>
       </c>
       <c r="B37" s="5" t="inlineStr">
@@ -1428,7 +1412,7 @@
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>2025-08-31</t>
+          <t>2025-04-22</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
@@ -1438,27 +1422,27 @@
       </c>
       <c r="E37" s="5" t="inlineStr">
         <is>
-          <t>175+280</t>
+          <t>175+285</t>
         </is>
       </c>
       <c r="F37" s="5" t="n">
-        <v>15</v>
+        <v>75</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="4" t="inlineStr">
         <is>
-          <t>Limpieza de Superfície de Concreto y Dispos. Drenaje T2</t>
+          <t>Remocion de Derrumbes T2</t>
         </is>
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>ml</t>
+          <t>m3</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2025-04-26</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
@@ -1468,81 +1452,305 @@
       </c>
       <c r="E38" s="5" t="inlineStr">
         <is>
-          <t>175+270</t>
+          <t>175+285</t>
         </is>
       </c>
       <c r="F38" s="5" t="n">
-        <v>100</v>
+        <v>135</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
         <is>
-          <t>Limpieza Manual de Cuneta de Vía T2</t>
+          <t>Remocion de Derrumbes T2</t>
         </is>
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>ml</t>
+          <t>m3</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-04-27</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>175+270</t>
+          <t>175+260</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
         <is>
-          <t>175+270</t>
+          <t>175+285</t>
         </is>
       </c>
       <c r="F39" s="5" t="n">
-        <v>120</v>
+        <v>195</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
         <is>
+          <t>Remocion de Derrumbes T2</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="inlineStr">
+        <is>
+          <t>m3</t>
+        </is>
+      </c>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>2025-05-11</t>
+        </is>
+      </c>
+      <c r="D40" s="5" t="inlineStr">
+        <is>
+          <t>175+260</t>
+        </is>
+      </c>
+      <c r="E40" s="5" t="inlineStr">
+        <is>
+          <t>175+285</t>
+        </is>
+      </c>
+      <c r="F40" s="5" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>Limpieza de Deslizamientos Menores &lt; 15 m3 T2</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="inlineStr">
+        <is>
+          <t>m3</t>
+        </is>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="D41" s="5" t="inlineStr">
+        <is>
+          <t>175+260</t>
+        </is>
+      </c>
+      <c r="E41" s="5" t="inlineStr">
+        <is>
+          <t>175+280</t>
+        </is>
+      </c>
+      <c r="F41" s="5" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>Limpieza de Superfície de Concreto y Dispos. Drenaje T2</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="inlineStr">
+        <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>2025-09-06</t>
+        </is>
+      </c>
+      <c r="D42" s="5" t="inlineStr">
+        <is>
+          <t>175+260</t>
+        </is>
+      </c>
+      <c r="E42" s="5" t="inlineStr">
+        <is>
+          <t>175+270</t>
+        </is>
+      </c>
+      <c r="F42" s="5" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>Pintura Chevron Guarda Vías T2</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="inlineStr">
+        <is>
+          <t>m2</t>
+        </is>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>2025-09-19</t>
+        </is>
+      </c>
+      <c r="D43" s="5" t="inlineStr">
+        <is>
+          <t>175+285</t>
+        </is>
+      </c>
+      <c r="E43" s="5" t="n"/>
+      <c r="F43" s="5" t="n">
+        <v>5.25</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>Reposición de Defensas Averiadas T2</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="inlineStr">
+        <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="C44" s="5" t="inlineStr">
+        <is>
+          <t>2025-09-19</t>
+        </is>
+      </c>
+      <c r="D44" s="5" t="inlineStr">
+        <is>
+          <t>175+285</t>
+        </is>
+      </c>
+      <c r="E44" s="5" t="n"/>
+      <c r="F44" s="5" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>Sellado de Juntas de Badenes T2</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="inlineStr">
+        <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="D45" s="5" t="inlineStr">
+        <is>
+          <t>175+260</t>
+        </is>
+      </c>
+      <c r="E45" s="5" t="n"/>
+      <c r="F45" s="5" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="inlineStr">
+        <is>
+          <t>Sellado de Juntas de Badenes T2</t>
+        </is>
+      </c>
+      <c r="B46" s="5" t="inlineStr">
+        <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="C46" s="5" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="D46" s="5" t="inlineStr">
+        <is>
+          <t>175+260</t>
+        </is>
+      </c>
+      <c r="E46" s="5" t="n"/>
+      <c r="F46" s="5" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>Limpieza Manual de Cuneta de Vía T2</t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="inlineStr">
+        <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>2025-11-21</t>
+        </is>
+      </c>
+      <c r="D47" s="5" t="inlineStr">
+        <is>
+          <t>175+270</t>
+        </is>
+      </c>
+      <c r="E47" s="5" t="inlineStr">
+        <is>
+          <t>175+270</t>
+        </is>
+      </c>
+      <c r="F47" s="5" t="n">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="4" t="inlineStr">
+        <is>
           <t>Limpieza de Cajas de Inspección Subdren T2</t>
         </is>
       </c>
-      <c r="B40" s="5" t="inlineStr">
+      <c r="B48" s="5" t="inlineStr">
         <is>
           <t>und</t>
         </is>
       </c>
-      <c r="C40" s="5" t="inlineStr">
+      <c r="C48" s="5" t="inlineStr">
         <is>
           <t>2025-11-27</t>
         </is>
       </c>
-      <c r="D40" s="5" t="inlineStr">
+      <c r="D48" s="5" t="inlineStr">
         <is>
           <t>175+270</t>
         </is>
       </c>
-      <c r="E40" s="5" t="inlineStr">
+      <c r="E48" s="5" t="inlineStr">
         <is>
           <t>175+270</t>
         </is>
       </c>
-      <c r="F40" s="5" t="n">
+      <c r="F48" s="5" t="n">
         <v>2</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="6">
     <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A10:F10"/>
-    <mergeCell ref="A13:F13"/>
     <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A9:F9"/>
+    <mergeCell ref="A17:F17"/>
+    <mergeCell ref="A12:F12"/>
     <mergeCell ref="A4:F4"/>
-    <mergeCell ref="A7:F7"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
